--- a/00 - DOCUMENTS/compras cablagem.xlsx
+++ b/00 - DOCUMENTS/compras cablagem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorio_Remoto\FPGAging_Lite\00 - DOCUMENTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio_remoto\FPGAging_Lite\00 - DOCUMENTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C60DD89-428A-4C13-8829-30389484AFC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE48E99-5BB3-434A-9C6E-ABD04BB4D6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11490" windowHeight="4470" xr2:uid="{C8FDF1B3-ECF4-4C3F-A18D-30EA7BB94828}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8FDF1B3-ECF4-4C3F-A18D-30EA7BB94828}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>ITEM</t>
   </si>
@@ -121,6 +130,15 @@
   </si>
   <si>
     <t>Cable Assembly Coaxial I-PEX MHF1 to I-PEX MHF1 0.81mm OD Coaxial Cable 7.874" (200.00mm)</t>
+  </si>
+  <si>
+    <t>44A0111-28-9</t>
+  </si>
+  <si>
+    <t>44A0111-28-9-DS-ND</t>
+  </si>
+  <si>
+    <t>28 AWG Hook-Up, Dual Wall Wire 7/36 White 600V Enter Number of Feet in Order Quantity</t>
   </si>
 </sst>
 </file>
@@ -472,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBBFFC4-90EC-4BD7-B8A8-68C6573F87E6}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
@@ -548,7 +566,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G11" si="0">F3*E3</f>
+        <f t="shared" ref="G3:G10" si="0">F3*E3</f>
         <v>0.65</v>
       </c>
     </row>
@@ -672,40 +690,65 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>1.1355999999999999</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>28.389999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D10" t="s">
         <v>31</v>
       </c>
-      <c r="E11">
+      <c r="E10">
         <v>2</v>
       </c>
-      <c r="F11">
+      <c r="F10">
         <v>1.7</v>
       </c>
-      <c r="G11">
+      <c r="G10">
         <f t="shared" si="0"/>
         <v>3.4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
         <v>17</v>
       </c>
-      <c r="G12">
-        <f>SUM(G2:G8)</f>
-        <v>106.47</v>
+      <c r="G11">
+        <f>SUM(G2:G10)</f>
+        <v>138.26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>